--- a/resultados/experimentos_entrenamiento.xlsx
+++ b/resultados/experimentos_entrenamiento.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CT4"/>
+  <dimension ref="A1:CU5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -908,6 +908,11 @@
           <t>test_tp</t>
         </is>
       </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>wandb</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -1246,6 +1251,7 @@
       <c r="CT2" t="n">
         <v>1556</v>
       </c>
+      <c r="CU2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -1584,6 +1590,7 @@
       <c r="CT3" t="n">
         <v>1427</v>
       </c>
+      <c r="CU3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -1921,6 +1928,352 @@
       </c>
       <c r="CT4" t="n">
         <v>1218</v>
+      </c>
+      <c r="CU4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>prueba_resnet50_final</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:54:08</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:58:59</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4.836991186936697</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>C:\Users\yeray\Desktop\UNIR\Semestre 2\TFM\TFM-UNIR\models\prueba_resnet50_final_best.pth</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>C:\Users\yeray\Desktop\UNIR\Semestre 2\TFM\TFM-UNIR\resultados\experimentos_entrenamiento.xlsx</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0.7596183441058787</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>{"Control": 0, "PD": 1}</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>1249</v>
+      </c>
+      <c r="N5" t="n">
+        <v>269</v>
+      </c>
+      <c r="O5" t="n">
+        <v>269</v>
+      </c>
+      <c r="P5" t="n">
+        <v>14968834</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>23512130</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>data_index.csv</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>data/PPMI_Procesado_2D</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>models</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>resultados/experimentos_entrenamiento.xlsx</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>['Control', 'PD']</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>adamw</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>plateau</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>layer4</t>
+        </is>
+      </c>
+      <c r="AK5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AN5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>prueba_resnet50_final</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:54:08</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="AR5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.1317389187185808</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.9585585585585585</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.9517320261437908</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.9809890986439777</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.9645751633986928</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.9727128921697864</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.8871770143548081</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.8866318656377666</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>9990</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>[[2197, 143], [271, 7379]]</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.9895460030165912</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.9964161072582707</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.9388888888888889</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0.9645751633986928</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2197</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>143</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>271</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>7379</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1.373591775136851</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.6358974358974359</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.5052525252525253</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0.7717323327079425</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0.7478787878787879</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0.7596183441058787</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0.0101606657079825</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0.0101394169835235</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>2145</v>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>[[130, 365], [416, 1234]]</t>
+        </is>
+      </c>
+      <c r="BU5" t="n">
+        <v>0.5194943373125191</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0.7740111814642383</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0.2626262626262627</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0.7478787878787879</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>130</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>365</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>416</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>1234</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>1.150413749794318</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0.6811188811188811</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0.5533729087965462</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.7873111782477341</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.7969418960244649</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.79209726443769</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.1082424952952021</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.1082056892778994</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>2145</v>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>[[158, 352], [332, 1303]]</t>
+        </is>
+      </c>
+      <c r="CM5" t="n">
+        <v>0.6042651556035258</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0.8117615563666154</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0.3098039215686275</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0.7969418960244649</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>158</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>352</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>332</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>1303</v>
+      </c>
+      <c r="CU5" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1934,7 +2287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ40"/>
+  <dimension ref="A1:AQ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7651,6 +8004,288 @@
       </c>
       <c r="AQ40" t="n">
         <v>1450</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>prueba_resnet50_final</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:54:08</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0.7375201288244766</v>
+      </c>
+      <c r="G41" t="b">
+        <v>1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.5040370247594348</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.7795795795795796</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.7307516339869281</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.8816195012608574</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.8226143790849674</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.8510954828239112</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.4327632708525154</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.4289312349301883</v>
+      </c>
+      <c r="P41" t="n">
+        <v>9990</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>[[1495, 845], [1357, 6293]]</t>
+        </is>
+      </c>
+      <c r="R41" t="n">
+        <v>0.8296744036645998</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.9373472684730444</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0.6388888888888888</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0.8226143790849674</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1495</v>
+      </c>
+      <c r="W41" t="n">
+        <v>845</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1357</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>6293</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.203256391799569</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.62004662004662</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.5338383838383839</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0.7869415807560137</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.693939393939394</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0.7375201288244766</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0.06104191329225139</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.05947625388371047</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>2145</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[[185, 310], [505, 1145]]</t>
+        </is>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0.5565889194980105</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0.7933071950594857</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0.3737373737373738</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0.693939393939394</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>185</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>310</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>505</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>prueba_resnet50_final</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-06-09 16:54:08</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>0.7596183441058787</v>
+      </c>
+      <c r="G42" t="b">
+        <v>1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1317389187185808</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.9585585585585585</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.9517320261437908</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.9809890986439777</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.9645751633986928</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.9727128921697864</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.8871770143548081</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.8866318656377666</v>
+      </c>
+      <c r="P42" t="n">
+        <v>9990</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>[[2197, 143], [271, 7379]]</t>
+        </is>
+      </c>
+      <c r="R42" t="n">
+        <v>0.9895460030165912</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.9964161072582707</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.9388888888888889</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.9645751633986928</v>
+      </c>
+      <c r="V42" t="n">
+        <v>2197</v>
+      </c>
+      <c r="W42" t="n">
+        <v>143</v>
+      </c>
+      <c r="X42" t="n">
+        <v>271</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>7379</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.373591775136851</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.6358974358974359</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.5052525252525253</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0.7717323327079425</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.7478787878787879</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0.7596183441058787</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0.0101606657079825</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.0101394169835235</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>2145</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[[130, 365], [416, 1234]]</t>
+        </is>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0.5194943373125191</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0.7740111814642383</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0.2626262626262627</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0.7478787878787879</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>130</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>365</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>416</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1234</v>
       </c>
     </row>
   </sheetData>

--- a/resultados/experimentos_entrenamiento.xlsx
+++ b/resultados/experimentos_entrenamiento.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU5"/>
+  <dimension ref="A1:CW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -913,6 +913,16 @@
           <t>wandb</t>
         </is>
       </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>roi</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>roi_frac</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -1252,6 +1262,8 @@
         <v>1556</v>
       </c>
       <c r="CU2" t="inlineStr"/>
+      <c r="CV2" t="inlineStr"/>
+      <c r="CW2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -1591,6 +1603,8 @@
         <v>1427</v>
       </c>
       <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr"/>
+      <c r="CW3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -1930,6 +1944,8 @@
         <v>1218</v>
       </c>
       <c r="CU4" t="inlineStr"/>
+      <c r="CV4" t="inlineStr"/>
+      <c r="CW4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2272,8 +2288,357 @@
       <c r="CT5" t="n">
         <v>1303</v>
       </c>
-      <c r="CU5" t="b">
+      <c r="CU5" t="n">
         <v>1</v>
+      </c>
+      <c r="CV5" t="inlineStr"/>
+      <c r="CW5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-06-19 17:24:54</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>47.75721781651179</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>/Users/luisazcoitipena/Desktop/Repo TFM/TFM-UNIR/models/resnet50_v2_best.pth</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>/Users/luisazcoitipena/Desktop/Repo TFM/TFM-UNIR/resultados/experimentos_entrenamiento.xlsx</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.7933884297520661</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>{"Control": 0, "PD": 1}</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>300</v>
+      </c>
+      <c r="N6" t="n">
+        <v>65</v>
+      </c>
+      <c r="O6" t="n">
+        <v>65</v>
+      </c>
+      <c r="P6" t="n">
+        <v>14968834</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>23512130</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>data_index.csv</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>data/PPMI_Procesado_2D_Atlas</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>models</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>resultados/experimentos_entrenamiento.xlsx</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>['Control', 'PD']</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>2</v>
+      </c>
+      <c r="X6" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>adamw</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>plateau</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>layer4</t>
+        </is>
+      </c>
+      <c r="AK6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AN6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.5e-05</v>
+      </c>
+      <c r="AR6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.07196777855892883</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.9754825247782994</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.9737311385459533</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.9905437352245863</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.9770919067215363</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.9837718389613977</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.9340289114629419</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.9336641181919745</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>9585</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>[[2227, 68], [167, 7123]]</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.9965818816476445</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.9988768717122346</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.9703703703703703</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.9770919067215363</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2227</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>68</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>167</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>7123</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>3.01556841091518</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.6715328467153284</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.4989285714285714</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.7659574468085106</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.8228571428571428</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.7933884297520661</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>-0.002377391058253659</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>-0.002341235001463327</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>2055</v>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>[[84, 396], [279, 1296]]</t>
+        </is>
+      </c>
+      <c r="BU6" t="n">
+        <v>0.4525482804232804</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.735736414516627</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0.8228571428571428</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>84</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>396</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>279</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>1296</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>2.262195858178058</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.7041362530413625</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.5534285159285159</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.7829964328180737</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.8442307692307692</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.8124614435533621</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.1185497366952772</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.1166726759846444</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>2055</v>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>[[130, 365], [243, 1317]]</t>
+        </is>
+      </c>
+      <c r="CM6" t="n">
+        <v>0.5736227661227662</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0.805498101829476</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0.2626262626262627</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0.8442307692307692</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>130</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>365</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>243</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>1317</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV6" t="b">
+        <v>1</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -2287,7 +2652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ42"/>
+  <dimension ref="A1:AQ75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8286,6 +8651,4659 @@
       </c>
       <c r="AQ42" t="n">
         <v>1234</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>0.5797546012269938</v>
+      </c>
+      <c r="G43" t="b">
+        <v>1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.6756509267730394</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.5889410537297861</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.5718308722666021</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.8064398097328943</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.6046639231824417</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.6911257447475698</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.1238413094296794</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.1129165239671729</v>
+      </c>
+      <c r="P43" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>[[1237, 1058], [2882, 4408]]</t>
+        </is>
+      </c>
+      <c r="R43" t="n">
+        <v>0.6045757312222252</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.8224076222607789</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0.5389978213507626</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0.6046639231824417</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1237</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1058</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2882</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>4408</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0.7332829232343502</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.4514583333333333</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0.7318489835430784</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0.5797546012269938</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>-0.08215423735433683</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>-0.06971773791373992</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[[203, 277], [819, 756]]</t>
+        </is>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0.4256838624338625</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0.7274089374854318</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0.4229166666666667</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>203</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>277</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>819</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>0.5485133020344288</v>
+      </c>
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.6192133478528831</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.6660406885758998</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.6617768094892278</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.8600105652403592</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.6699588477366255</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.7531806615776081</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.2809954690296183</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.260827991296627</v>
+      </c>
+      <c r="P44" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>[[1500, 795], [2406, 4884]]</t>
+        </is>
+      </c>
+      <c r="R44" t="n">
+        <v>0.7191807501845426</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.8813456158123103</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0.6535947712418301</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0.6699588477366255</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1500</v>
+      </c>
+      <c r="W44" t="n">
+        <v>795</v>
+      </c>
+      <c r="X44" t="n">
+        <v>2406</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>4884</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.8166757334757896</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.4384428223844282</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.4308730158730159</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0.7145769622833843</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.4450793650793651</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0.5485133020344288</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>-0.1171121243554027</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>-0.09666902512451281</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[[200, 280], [874, 701]]</t>
+        </is>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0.4168505291005291</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0.7191087239116816</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0.4450793650793651</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>200</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>280</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>874</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>0.5991156963890936</v>
+      </c>
+      <c r="G45" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.5403689671849981</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.7229003651538862</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.7224441216815944</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.891914749661705</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.7233196159122085</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.798818360854416</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.3905065848075183</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.3689860329400427</v>
+      </c>
+      <c r="P45" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>[[1656, 639], [2017, 5273]]</t>
+        </is>
+      </c>
+      <c r="R45" t="n">
+        <v>0.8000586651365317</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.9242496809381489</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0.7215686274509804</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0.7233196159122085</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1656</v>
+      </c>
+      <c r="W45" t="n">
+        <v>639</v>
+      </c>
+      <c r="X45" t="n">
+        <v>2017</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>5273</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.096920678273315</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0.4705596107055961</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0.4185119047619048</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0.713784021071115</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.5161904761904762</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0.5991156963890936</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>-0.1387316210510317</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>-0.1238652471574628</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[[154, 326], [762, 813]]</t>
+        </is>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0.3636785714285714</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0.6854955186705401</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0.3208333333333334</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>0.5161904761904762</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>154</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>326</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>762</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>0.6203670385030586</v>
+      </c>
+      <c r="G46" t="b">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.4814437440241384</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.7669274908711529</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.7648228838860647</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.9107897302567436</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.7688614540466392</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.8338292174947932</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.4714672284484557</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.4528514067307825</v>
+      </c>
+      <c r="P46" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>[[1746, 549], [1685, 5605]]</t>
+        </is>
+      </c>
+      <c r="R46" t="n">
+        <v>0.849223486376718</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.9432986142692135</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0.7607843137254902</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0.7688614540466392</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1746</v>
+      </c>
+      <c r="W46" t="n">
+        <v>549</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1685</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>5605</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1.173547099106503</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0.4866180048661801</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.4174007936507936</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0.7159468438538206</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.5473015873015873</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0.6203670385030586</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>-0.1419020744330097</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>-0.1302127726124662</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[[138, 342], [713, 862]]</t>
+        </is>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0.3889232804232804</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0.708474048364489</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>0.5473015873015873</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>138</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>342</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>713</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>5</v>
+      </c>
+      <c r="D47" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>0.6518518518518519</v>
+      </c>
+      <c r="G47" t="b">
+        <v>1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.4198643385928686</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.8066770996348461</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.800956184943113</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.9246992657397282</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.8119341563786008</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.8646556131765394</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.5453532863222409</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.531392362681788</v>
+      </c>
+      <c r="P47" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>[[1813, 482], [1371, 5919]]</t>
+        </is>
+      </c>
+      <c r="R47" t="n">
+        <v>0.8887744873898348</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.959960015960148</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0.7899782135076253</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0.8119341563786008</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1813</v>
+      </c>
+      <c r="W47" t="n">
+        <v>482</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1371</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>5919</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.424285741212014</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0.5197080291970803</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0.4433333333333334</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.5866666666666667</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0.6518518518518519</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>-0.09845770835962905</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>-0.09228159457167084</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[[144, 336], [651, 924]]</t>
+        </is>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0.40919708994709</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0.6991539149394708</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>0.5866666666666667</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>144</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>336</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>651</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>6</v>
+      </c>
+      <c r="D48" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>0.7128777923784494</v>
+      </c>
+      <c r="G48" t="b">
+        <v>1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.3635025555072629</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.8387063119457485</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.8372387638182845</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.9415744157441575</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.8400548696844993</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.8879222850514716</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.6162919258397377</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.6036498617038947</v>
+      </c>
+      <c r="P48" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>[[1915, 380], [1166, 6124]]</t>
+        </is>
+      </c>
+      <c r="R48" t="n">
+        <v>0.9182342481269294</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.9712457769271422</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0.8344226579520697</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0.8400548696844993</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1915</v>
+      </c>
+      <c r="W48" t="n">
+        <v>380</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1166</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>6124</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.632885660626302</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0.5746958637469587</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0.7385976855003403</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.6888888888888889</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0.7128777923784494</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>-0.1041258794293341</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>-0.10318966629199</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[[96, 384], [490, 1085]]</t>
+        </is>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0.3983293650793651</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>0.7027646021808276</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>0.6888888888888889</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>96</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>384</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>490</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>7</v>
+      </c>
+      <c r="D49" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0.7086666666666667</v>
+      </c>
+      <c r="G49" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.3212144610592021</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.8615545122587376</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.858081174856774</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.9486832204665162</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.8647462277091906</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.9047721564406171</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.6627434384809289</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.6532634096973042</v>
+      </c>
+      <c r="P49" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>[[1954, 341], [986, 6304]]</t>
+        </is>
+      </c>
+      <c r="R49" t="n">
+        <v>0.9365872909139269</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0.978071712019399</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0.8514161220043573</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0.8647462277091906</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1954</v>
+      </c>
+      <c r="W49" t="n">
+        <v>341</v>
+      </c>
+      <c r="X49" t="n">
+        <v>986</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>6304</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.720058218174027</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0.5746958637469587</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0.4603769841269841</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0.7459649122807017</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.6749206349206349</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0.7086666666666667</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>-0.07272114611738284</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>-0.0714809843400448</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[[118, 362], [512, 1063]]</t>
+        </is>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0.4198730158730158</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>0.7083211579078603</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>0.2458333333333333</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>0.6749206349206349</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>118</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>362</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>512</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>8</v>
+      </c>
+      <c r="D50" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>0.726797385620915</v>
+      </c>
+      <c r="G50" t="b">
+        <v>1</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.2868879696137593</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.8797078768909755</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.8774792221415315</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.9566899836285161</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.8817558299039781</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.9176957670069241</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.703700310452512</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.6956618721350847</v>
+      </c>
+      <c r="P50" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>[[2004, 291], [862, 6428]]</t>
+        </is>
+      </c>
+      <c r="R50" t="n">
+        <v>0.9498980009623115</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0.9826760658205912</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0.873202614379085</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0.8817558299039781</v>
+      </c>
+      <c r="V50" t="n">
+        <v>2004</v>
+      </c>
+      <c r="W50" t="n">
+        <v>291</v>
+      </c>
+      <c r="X50" t="n">
+        <v>862</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>6428</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1.949331635338257</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0.5931873479318734</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0.4644742063492063</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0.7488215488215488</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.706031746031746</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0.726797385620915</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>-0.06714814624911292</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>-0.06670392102076939</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[[107, 373], [463, 1112]]</t>
+        </is>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0.4113657407407407</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>0.7032172433798412</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>0.2229166666666667</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>0.706031746031746</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>107</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>373</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>463</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>9</v>
+      </c>
+      <c r="D51" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>0.6526540790879943</v>
+      </c>
+      <c r="G51" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.2690596239263339</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.8870109546165884</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.8840716533526991</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.9587583148558758</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.8897119341563786</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.9229455709711847</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.7193477757806689</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.7123183119142489</v>
+      </c>
+      <c r="P51" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>[[2016, 279], [804, 6486]]</t>
+        </is>
+      </c>
+      <c r="R51" t="n">
+        <v>0.9557643950736826</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0.9848809312800784</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.8784313725490196</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0.8897119341563786</v>
+      </c>
+      <c r="V51" t="n">
+        <v>2016</v>
+      </c>
+      <c r="W51" t="n">
+        <v>279</v>
+      </c>
+      <c r="X51" t="n">
+        <v>804</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>6486</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1.727317359093622</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0.5255474452554745</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0.4616269841269841</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0.7435064935064936</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.5815873015873015</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0.6526540790879943</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>-0.06626917365743708</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>-0.06147537726777852</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[[164, 316], [659, 916]]</t>
+        </is>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0.4377592592592593</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>0.7164542678661971</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0.3416666666666667</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>0.5815873015873015</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>164</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>316</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>659</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>10</v>
+      </c>
+      <c r="D52" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>0.6708595387840671</v>
+      </c>
+      <c r="G52" t="b">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.2370959116570578</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.9074595722483046</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.9034858387799565</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.9652666763551809</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.9111111111111111</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.9374073812716111</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.7652164173075995</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.7605373527052051</v>
+      </c>
+      <c r="P52" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>[[2056, 239], [648, 6642]]</t>
+        </is>
+      </c>
+      <c r="R52" t="n">
+        <v>0.9663941412565635</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0.9882678467586905</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0.8958605664488017</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0.9111111111111111</v>
+      </c>
+      <c r="V52" t="n">
+        <v>2056</v>
+      </c>
+      <c r="W52" t="n">
+        <v>239</v>
+      </c>
+      <c r="X52" t="n">
+        <v>648</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>6642</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>2.132002736762202</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0.5416058394160584</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0.4641369047619048</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0.745920745920746</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.6095238095238096</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0.6708595387840671</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>-0.06272905997389409</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>-0.05934791174152876</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[[153, 327], [615, 960]]</t>
+        </is>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0.4207037037037037</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>0.7038702121496079</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>0.6095238095238096</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>153</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>327</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>615</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>11</v>
+      </c>
+      <c r="D53" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>0.7330494595479856</v>
+      </c>
+      <c r="G53" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.2215722707857611</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.909546165884194</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.9060518034374243</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.9664488017429194</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.9127572016460905</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.9388359788359788</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.7704291281287494</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.7658049420761285</v>
+      </c>
+      <c r="P53" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>[[2064, 231], [636, 6654]]</t>
+        </is>
+      </c>
+      <c r="R53" t="n">
+        <v>0.9705359955291368</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0.9901749678864243</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0.8993464052287582</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0.9127572016460905</v>
+      </c>
+      <c r="V53" t="n">
+        <v>2064</v>
+      </c>
+      <c r="W53" t="n">
+        <v>231</v>
+      </c>
+      <c r="X53" t="n">
+        <v>636</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>6654</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.929542958823434</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0.6034063260340633</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0.4812797619047619</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0.7571041948579161</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.7104761904761905</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0.7330494595479856</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>-0.03525146236268212</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>-0.03498299051732934</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[[121, 359], [456, 1119]]</t>
+        </is>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0.4436375661375661</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>0.7283903327237322</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0.2520833333333333</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>0.7104761904761905</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>121</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>359</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>456</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>12</v>
+      </c>
+      <c r="D54" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>0.6734194900454069</v>
+      </c>
+      <c r="G54" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.1943716339848597</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.9199791340636411</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.9160453481804245</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.9697537087714244</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.9235939643347051</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.9461111501440315</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.7946681115650159</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.7911115884602549</v>
+      </c>
+      <c r="P54" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>[[2085, 210], [557, 6733]]</t>
+        </is>
+      </c>
+      <c r="R54" t="n">
+        <v>0.9771588501274614</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0.9923798367656862</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0.9084967320261438</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0.9235939643347051</v>
+      </c>
+      <c r="V54" t="n">
+        <v>2085</v>
+      </c>
+      <c r="W54" t="n">
+        <v>210</v>
+      </c>
+      <c r="X54" t="n">
+        <v>557</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>6733</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1.779700595270978</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0.5450121654501217</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0.4685317460317461</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0.7484472049689441</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.6120634920634921</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0.6734194900454069</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>-0.05505641469366844</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>-0.05210634820247906</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>[[156, 324], [611, 964]]</t>
+        </is>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0.4450601851851852</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>0.7334094551235608</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>0.6120634920634921</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>156</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>324</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>611</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>13</v>
+      </c>
+      <c r="D55" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>0.7533546325878594</v>
+      </c>
+      <c r="G55" t="b">
+        <v>1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.1792066419325151</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.9293688054251434</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.9280400225933996</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.9754133716750539</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.9305898491083676</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.9524745524745525</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.8187344066753853</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.8153080632456629</v>
+      </c>
+      <c r="P55" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>[[2124, 171], [506, 6784]]</t>
+        </is>
+      </c>
+      <c r="R55" t="n">
+        <v>0.9804919742626513</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0.9935752627245142</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0.9254901960784314</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0.9305898491083676</v>
+      </c>
+      <c r="V55" t="n">
+        <v>2124</v>
+      </c>
+      <c r="W55" t="n">
+        <v>171</v>
+      </c>
+      <c r="X55" t="n">
+        <v>506</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>6784</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>2.27344913006989</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0.624330900243309</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0.4826190476190476</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0.7581993569131833</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.7485714285714286</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>0.7533546325878594</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>-0.03427790448488731</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>-0.03426559749657732</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>[[104, 376], [396, 1179]]</t>
+        </is>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0.4434993386243386</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>0.7253733528905241</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>0.2166666666666667</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>0.7485714285714286</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>104</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>376</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>396</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>14</v>
+      </c>
+      <c r="D56" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>0.727986906710311</v>
+      </c>
+      <c r="G56" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.1682512390408344</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.9344809598330726</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.9302065682239975</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.9745014245014245</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.9384087791495199</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.9561146051712089</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.829373014864344</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.8270777583866589</v>
+      </c>
+      <c r="P56" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>[[2116, 179], [449, 6841]]</t>
+        </is>
+      </c>
+      <c r="R56" t="n">
+        <v>0.9827814387452892</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0.9943443376657822</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0.922004357298475</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0.9384087791495199</v>
+      </c>
+      <c r="V56" t="n">
+        <v>2116</v>
+      </c>
+      <c r="W56" t="n">
+        <v>179</v>
+      </c>
+      <c r="X56" t="n">
+        <v>449</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>6841</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>2.241590544777195</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0.5956204379562043</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0.4696825396825397</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0.7513513513513513</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.706031746031746</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0.727986906710311</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>-0.05715035483238407</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>-0.05673179560959762</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[[112, 368], [463, 1112]]</t>
+        </is>
+      </c>
+      <c r="AJ56" t="n">
+        <v>0.4454814814814815</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>0.7367732111268439</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>0.706031746031746</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>112</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>368</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>463</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>15</v>
+      </c>
+      <c r="D57" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>0.6792584819867087</v>
+      </c>
+      <c r="G57" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.1486907621924306</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.9451225873761085</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.9424271766319696</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.9795802609188883</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.947599451303155</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.9633245014642309</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.8563536521622761</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.8544957259629246</v>
+      </c>
+      <c r="P57" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>[[2151, 144], [382, 6908]]</t>
+        </is>
+      </c>
+      <c r="R57" t="n">
+        <v>0.9862966250362361</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0.9954337817772341</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0.9372549019607843</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0.947599451303155</v>
+      </c>
+      <c r="V57" t="n">
+        <v>2151</v>
+      </c>
+      <c r="W57" t="n">
+        <v>144</v>
+      </c>
+      <c r="X57" t="n">
+        <v>382</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>6908</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>1.940690221925722</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0.5537712895377129</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0.4822123015873016</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0.7562305295950156</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.6165079365079366</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0.6792584819867087</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>-0.03108858460187369</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>-0.02938308628925856</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[[167, 313], [604, 971]]</t>
+        </is>
+      </c>
+      <c r="AJ57" t="n">
+        <v>0.4728763227513227</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>0.7577102635312284</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>0.3479166666666667</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>0.6165079365079366</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>167</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>313</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>604</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>16</v>
+      </c>
+      <c r="D58" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>0.7715189873417722</v>
+      </c>
+      <c r="G58" t="b">
+        <v>1</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.1417363831756882</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.9456442357850808</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.9439643347050755</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.9806845618520097</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.9471879286694102</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.9636452445746982</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.8581386488113341</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.856107020184928</v>
+      </c>
+      <c r="P58" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>[[2159, 136], [385, 6905]]</t>
+        </is>
+      </c>
+      <c r="R58" t="n">
+        <v>0.9879708676642429</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0.9961099139125553</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0.9407407407407408</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0.9471879286694102</v>
+      </c>
+      <c r="V58" t="n">
+        <v>2159</v>
+      </c>
+      <c r="W58" t="n">
+        <v>136</v>
+      </c>
+      <c r="X58" t="n">
+        <v>385</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>6905</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>2.282322886622445</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0.648661800486618</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0.505734126984127</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>0.7690851735015772</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.773968253968254</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>0.7715189873417722</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>0.01155299638584398</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0.01155191366043773</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[[114, 366], [356, 1219]]</t>
+        </is>
+      </c>
+      <c r="AJ58" t="n">
+        <v>0.4799484126984127</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>0.7472523977008225</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>0.773968253968254</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>114</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>366</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>356</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>17</v>
+      </c>
+      <c r="D59" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>0.7748822605965463</v>
+      </c>
+      <c r="G59" t="b">
+        <v>1</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.1434023147955125</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.9443922796035472</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.94239490034697</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.9799687455604489</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.9462277091906721</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.96280270779538</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.8548905857312319</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.8528351487670476</v>
+      </c>
+      <c r="P59" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>[[2154, 141], [392, 6898]]</t>
+        </is>
+      </c>
+      <c r="R59" t="n">
+        <v>0.9873968877293335</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0.9959057093248527</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0.938562091503268</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0.9462277091906721</v>
+      </c>
+      <c r="V59" t="n">
+        <v>2154</v>
+      </c>
+      <c r="W59" t="n">
+        <v>141</v>
+      </c>
+      <c r="X59" t="n">
+        <v>392</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>6898</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>2.371397998559214</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0.6510948905109489</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0.5000793650793651</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>0.7664596273291926</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.7834920634920635</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>0.7748822605965463</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>0.0001630524785186992</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0.0001628581607205914</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>[[104, 376], [341, 1234]]</t>
+        </is>
+      </c>
+      <c r="AJ59" t="n">
+        <v>0.4680066137566138</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>0.7377966562938056</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>0.2166666666666667</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>0.7834920634920635</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>104</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>376</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>341</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>18</v>
+      </c>
+      <c r="D60" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>0.7334866907656917</v>
+      </c>
+      <c r="G60" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.1220669306406579</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.9579551382368284</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.9577301702574034</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.9861640547790484</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.958161865569273</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.9719613163570584</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.8894926629016746</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.88802006895769</v>
+      </c>
+      <c r="P60" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>[[2197, 98], [305, 6985]]</t>
+        </is>
+      </c>
+      <c r="R60" t="n">
+        <v>0.990803290985652</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0.9970457161296495</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0.9572984749455338</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0.958161865569273</v>
+      </c>
+      <c r="V60" t="n">
+        <v>2197</v>
+      </c>
+      <c r="W60" t="n">
+        <v>98</v>
+      </c>
+      <c r="X60" t="n">
+        <v>305</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>6985</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>2.45942379123103</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0.6053527980535279</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0.4876190476190476</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0.7602179836512262</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>0.7334866907656917</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>-0.02319331723428776</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>-0.02298109767887224</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>[[128, 352], [459, 1116]]</t>
+        </is>
+      </c>
+      <c r="AJ60" t="n">
+        <v>0.458494708994709</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>0.7276421333506229</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>128</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>352</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>459</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>19</v>
+      </c>
+      <c r="D61" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>0.7601895734597156</v>
+      </c>
+      <c r="G61" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.1175265854800749</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.9562858633281168</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.9551399983861857</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.9847608296881615</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.9573388203017833</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.9708562286986159</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.884917278436498</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.8835067411726468</v>
+      </c>
+      <c r="P61" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>[[2187, 108], [311, 6979]]</t>
+        </is>
+      </c>
+      <c r="R61" t="n">
+        <v>0.9913812157998393</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0.9972051016744221</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0.9529411764705882</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0.9573388203017833</v>
+      </c>
+      <c r="V61" t="n">
+        <v>2187</v>
+      </c>
+      <c r="W61" t="n">
+        <v>108</v>
+      </c>
+      <c r="X61" t="n">
+        <v>311</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>6979</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>2.619665011292247</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0.6306569343065693</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0.4787797619047619</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>0.7566037735849057</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.7638095238095238</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>0.7601895734597156</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>-0.04291569076603947</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>-0.04290657439446366</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>[[93, 387], [372, 1203]]</t>
+        </is>
+      </c>
+      <c r="AJ61" t="n">
+        <v>0.456952380952381</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>0.7288560703302044</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>0.19375</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>0.7638095238095238</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>93</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>387</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>372</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>20</v>
+      </c>
+      <c r="D62" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>0.7426351570087407</v>
+      </c>
+      <c r="G62" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.1102858081432793</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.9595200834637454</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.9586096990236423</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.9860563380281691</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.9603566529492455</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.9730368311327311</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.8931737876119417</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.8919220055710306</v>
+      </c>
+      <c r="P62" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>[[2196, 99], [289, 7001]]</t>
+        </is>
+      </c>
+      <c r="R62" t="n">
+        <v>0.9923731736254935</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0.9975131296064481</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0.9568627450980393</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0.9603566529492455</v>
+      </c>
+      <c r="V62" t="n">
+        <v>2196</v>
+      </c>
+      <c r="W62" t="n">
+        <v>99</v>
+      </c>
+      <c r="X62" t="n">
+        <v>289</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>7001</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>2.67989063216532</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0.6131386861313869</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0.4818353174603175</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>0.7575957727873184</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.7282539682539683</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>0.7426351570087407</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>-0.03490254819603759</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>-0.03479235746249509</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[[113, 367], [428, 1147]]</t>
+        </is>
+      </c>
+      <c r="AJ62" t="n">
+        <v>0.4572136243386244</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>0.7296342037109931</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>0.2354166666666667</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>0.7282539682539683</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>113</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>367</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>428</v>
+      </c>
+      <c r="AQ62" t="n">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>21</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.5e-05</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>0.7680151706700379</v>
+      </c>
+      <c r="G63" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.1008165781346845</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.9633802816901409</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.9614459775679819</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.9864012337025094</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.9651577503429355</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.9756638702073078</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.9026297104544357</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.9017578024906473</v>
+      </c>
+      <c r="P63" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>[[2198, 97], [254, 7036]]</t>
+        </is>
+      </c>
+      <c r="R63" t="n">
+        <v>0.9936980553538287</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0.9979755925364444</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0.9577342047930283</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0.9651577503429355</v>
+      </c>
+      <c r="V63" t="n">
+        <v>2198</v>
+      </c>
+      <c r="W63" t="n">
+        <v>97</v>
+      </c>
+      <c r="X63" t="n">
+        <v>254</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>7036</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>2.834093619669151</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0.6428223844282238</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0.4961309523809524</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0.7646318439269981</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>0.7680151706700379</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>-0.007818799227497075</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>-0.007817354527050124</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[[106, 374], [360, 1215]]</t>
+        </is>
+      </c>
+      <c r="AJ63" t="n">
+        <v>0.470702380952381</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>0.7399867269648923</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>0.2208333333333333</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>106</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>374</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>360</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>22</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.5e-05</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>0.7771215418091389</v>
+      </c>
+      <c r="G64" t="b">
+        <v>1</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.08192541901183489</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.9684924360980699</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.9680908577422739</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.9894928551414962</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.9688614540466393</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.9790684779595231</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.9162416025258118</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.9154108346088905</v>
+      </c>
+      <c r="P64" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>[[2220, 75], [227, 7063]]</t>
+        </is>
+      </c>
+      <c r="R64" t="n">
+        <v>0.9960603805613085</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0.9987533129472025</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0.9673202614379085</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0.9688614540466393</v>
+      </c>
+      <c r="V64" t="n">
+        <v>2220</v>
+      </c>
+      <c r="W64" t="n">
+        <v>75</v>
+      </c>
+      <c r="X64" t="n">
+        <v>227</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>7063</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>2.876357154196486</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0.6510948905109489</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0.4884920634920635</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>0.7612667478684531</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0.7936507936507936</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>0.7771215418091389</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>-0.02430114564493378</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>-0.02418959638824303</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[[88, 392], [325, 1250]]</t>
+        </is>
+      </c>
+      <c r="AJ64" t="n">
+        <v>0.4592347883597884</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>0.7356450882831242</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>0.1833333333333333</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>0.7936507936507936</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>88</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>392</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>325</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>23</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.5e-05</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>0.76109537299339</v>
+      </c>
+      <c r="G65" t="b">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.0861781760241815</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.9695357329160146</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.967433228435407</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.988277979346916</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.9714677640603566</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.9798007747648035</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.9184348412281284</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.9178761566738497</v>
+      </c>
+      <c r="P65" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>[[2211, 84], [208, 7082]]</t>
+        </is>
+      </c>
+      <c r="R65" t="n">
+        <v>0.9950466661287286</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0.9982899971515861</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0.9633986928104575</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0.9714677640603566</v>
+      </c>
+      <c r="V65" t="n">
+        <v>2211</v>
+      </c>
+      <c r="W65" t="n">
+        <v>84</v>
+      </c>
+      <c r="X65" t="n">
+        <v>208</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>7082</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>2.95269944778034</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0.6306569343065693</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0.4744345238095238</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>0.7546816479400749</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0.7676190476190476</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>0.76109537299339</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>-0.05218725127440063</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>-0.0521506845156785</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[[87, 393], [366, 1209]]</t>
+        </is>
+      </c>
+      <c r="AJ65" t="n">
+        <v>0.439675925925926</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>0.7265673973434523</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>0.18125</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>0.7676190476190476</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>87</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>393</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>366</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>24</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.5e-05</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>0.7917563826514918</v>
+      </c>
+      <c r="G66" t="b">
+        <v>1</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.07497091754050571</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.975169535732916</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.9744210441378197</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.9913600891861761</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.9758573388203018</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.9835476289229919</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.9334465066905741</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.9329651933131808</v>
+      </c>
+      <c r="P66" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>[[2233, 62], [176, 7114]]</t>
+        </is>
+      </c>
+      <c r="R66" t="n">
+        <v>0.9964134472566651</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0.9988010851488142</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0.9729847494553376</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0.9758573388203018</v>
+      </c>
+      <c r="V66" t="n">
+        <v>2233</v>
+      </c>
+      <c r="W66" t="n">
+        <v>62</v>
+      </c>
+      <c r="X66" t="n">
+        <v>176</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>7114</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>2.793336340168677</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0.6705596107055961</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0.5033630952380952</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>0.7678997613365155</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0.8171428571428572</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>0.7917563826514918</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>0.007337928021093901</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>0.007257002793624956</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[[91, 389], [288, 1287]]</t>
+        </is>
+      </c>
+      <c r="AJ66" t="n">
+        <v>0.4661078042328042</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>0.7414621443481499</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>0.1895833333333333</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>0.8171428571428572</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>91</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>389</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>288</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>25</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.5e-05</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>0.7933884297520661</v>
+      </c>
+      <c r="G67" t="b">
+        <v>1</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.07196777855892883</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.9754825247782994</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.9737311385459533</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.9905437352245863</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.9770919067215363</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.9837718389613977</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.9340289114629419</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.9336641181919745</v>
+      </c>
+      <c r="P67" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>[[2227, 68], [167, 7123]]</t>
+        </is>
+      </c>
+      <c r="R67" t="n">
+        <v>0.9965818816476445</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0.9988768717122346</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0.9703703703703703</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0.9770919067215363</v>
+      </c>
+      <c r="V67" t="n">
+        <v>2227</v>
+      </c>
+      <c r="W67" t="n">
+        <v>68</v>
+      </c>
+      <c r="X67" t="n">
+        <v>167</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>7123</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>3.01556841091518</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0.6715328467153284</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0.4989285714285714</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>0.7659574468085106</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0.8228571428571428</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>0.7933884297520661</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>-0.002377391058253659</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>-0.002341235001463327</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[[84, 396], [279, 1296]]</t>
+        </is>
+      </c>
+      <c r="AJ67" t="n">
+        <v>0.4525482804232804</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>0.735736414516627</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>0.8228571428571428</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>84</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>396</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>279</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>26</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.5e-05</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>0.7703842549203374</v>
+      </c>
+      <c r="G68" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.06664654458787955</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.9768388106416276</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.9764141047365449</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.9922005571030641</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.9772290809327846</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.9846579129232895</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.9378857838558801</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.9374350017862104</v>
+      </c>
+      <c r="P68" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>[[2239, 56], [166, 7124]]</t>
+        </is>
+      </c>
+      <c r="R68" t="n">
+        <v>0.9972797068835155</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0.9991275547295182</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0.9755991285403051</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0.9772290809327846</v>
+      </c>
+      <c r="V68" t="n">
+        <v>2239</v>
+      </c>
+      <c r="W68" t="n">
+        <v>56</v>
+      </c>
+      <c r="X68" t="n">
+        <v>166</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>7124</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>2.969032217986392</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0.6423357664233577</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0.4820535714285714</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>0.7583025830258303</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0.7828571428571428</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>0.7703842549203374</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>-0.03736629270185123</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>-0.03726938409716007</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[[87, 393], [342, 1233]]</t>
+        </is>
+      </c>
+      <c r="AJ68" t="n">
+        <v>0.4505760582010582</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>0.7350764579247343</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>0.18125</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>0.7828571428571428</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>87</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>393</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>342</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>27</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.5e-05</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>0.775497512437811</v>
+      </c>
+      <c r="G69" t="b">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.06814883920593875</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.9763171622326552</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.974876946663439</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.9910999860937283</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.9776406035665295</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.9843242869967543</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.936288036569232</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.9359223609769285</v>
+      </c>
+      <c r="P69" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>[[2231, 64], [163, 7127]]</t>
+        </is>
+      </c>
+      <c r="R69" t="n">
+        <v>0.9971805469634889</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0.9991008791479834</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0.9721132897603486</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0.9776406035665295</v>
+      </c>
+      <c r="V69" t="n">
+        <v>2231</v>
+      </c>
+      <c r="W69" t="n">
+        <v>64</v>
+      </c>
+      <c r="X69" t="n">
+        <v>163</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>7127</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>3.090811483703391</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0.648661800486618</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0.4854563492063492</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>0.7599024984765387</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0.7917460317460318</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0.775497512437811</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>-0.03068385137919505</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>-0.0305473943030985</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[[86, 394], [328, 1247]]</t>
+        </is>
+      </c>
+      <c r="AJ69" t="n">
+        <v>0.4502817460317461</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>0.7326662136891744</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>0.1791666666666667</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>0.7917460317460318</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>86</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>394</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>328</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>28</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.5e-05</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>0.756120826709062</v>
+      </c>
+      <c r="G70" t="b">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.06924509463455755</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.9750652060511216</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.9734567901234568</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.9905384722415472</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.9765432098765432</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.9834910547765421</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.932968632186828</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.9325746708997064</v>
+      </c>
+      <c r="P70" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>[[2227, 68], [171, 7119]]</t>
+        </is>
+      </c>
+      <c r="R70" t="n">
+        <v>0.9970543108266017</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0.9990735278118387</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0.9703703703703703</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0.9765432098765432</v>
+      </c>
+      <c r="V70" t="n">
+        <v>2227</v>
+      </c>
+      <c r="W70" t="n">
+        <v>68</v>
+      </c>
+      <c r="X70" t="n">
+        <v>171</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>7119</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>2.75471302064956</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0.6267639902676398</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0.4805853174603174</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>0.7573248407643313</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0.7549206349206349</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>0.756120826709062</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>-0.03869015694813137</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>-0.03868927000444811</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>[[99, 381], [386, 1189]]</t>
+        </is>
+      </c>
+      <c r="AJ70" t="n">
+        <v>0.45405291005291</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>0.739215133856321</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>0.20625</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>0.7549206349206349</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>99</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>381</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>386</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>29</v>
+      </c>
+      <c r="D71" t="n">
+        <v>4.5e-06</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>0.7644641163452418</v>
+      </c>
+      <c r="G71" t="b">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.0622170477639155</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.9793427230046948</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.9776123618171548</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.9918169209431346</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.9809327846364884</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.9863448275862069</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.9441939739155315</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.9439518379714537</v>
+      </c>
+      <c r="P71" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>[[2236, 59], [139, 7151]]</t>
+        </is>
+      </c>
+      <c r="R71" t="n">
+        <v>0.9975651129221694</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0.9992335158410506</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0.9742919389978214</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0.9809327846364884</v>
+      </c>
+      <c r="V71" t="n">
+        <v>2236</v>
+      </c>
+      <c r="W71" t="n">
+        <v>59</v>
+      </c>
+      <c r="X71" t="n">
+        <v>139</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>7151</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>2.897289504912068</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0.6374695863746959</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0.4890178571428572</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>0.7613350125944585</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0.7676190476190476</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>0.7644641163452418</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>-0.02217656577167789</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>-0.02217303782636137</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>[[101, 379], [366, 1209]]</t>
+        </is>
+      </c>
+      <c r="AJ71" t="n">
+        <v>0.4608498677248677</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>0.7379895338079989</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>0.2104166666666667</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>0.7676190476190476</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>101</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>379</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>366</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>30</v>
+      </c>
+      <c r="D72" t="n">
+        <v>4.5e-06</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>0.7661315706641486</v>
+      </c>
+      <c r="G72" t="b">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.05843881143526168</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.9795513823682838</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.9787944807552651</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.9927757710475132</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.980246913580247</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.9864715626725566</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.9449353790448358</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.9446160213958227</v>
+      </c>
+      <c r="P72" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>[[2243, 52], [144, 7146]]</t>
+        </is>
+      </c>
+      <c r="R72" t="n">
+        <v>0.997996419723201</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0.9993677734504641</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0.9773420479302832</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0.980246913580247</v>
+      </c>
+      <c r="V72" t="n">
+        <v>2243</v>
+      </c>
+      <c r="W72" t="n">
+        <v>52</v>
+      </c>
+      <c r="X72" t="n">
+        <v>144</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>7146</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>2.943492868752955</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0.6384428223844282</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0.4853075396825396</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>0.7596754057428214</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>0.7726984126984127</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>0.7661315706641486</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>-0.02999197483018523</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>-0.02997095994090793</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>[[95, 385], [358, 1217]]</t>
+        </is>
+      </c>
+      <c r="AJ72" t="n">
+        <v>0.4545800264550264</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>0.7345707170550188</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>0.1979166666666667</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>0.7726984126984127</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>385</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>358</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>31</v>
+      </c>
+      <c r="D73" t="n">
+        <v>4.5e-06</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>0.7606349206349207</v>
+      </c>
+      <c r="G73" t="b">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.0603500837268746</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.9780907668231612</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.9778342612765271</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.9927616926503341</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.9783264746227709</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.9854912256459859</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0.9412026664121487</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.940782105154459</v>
+      </c>
+      <c r="P73" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>[[2243, 52], [158, 7132]]</t>
+        </is>
+      </c>
+      <c r="R73" t="n">
+        <v>0.9977688719139538</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0.9993016469322969</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0.9773420479302832</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0.9783264746227709</v>
+      </c>
+      <c r="V73" t="n">
+        <v>2243</v>
+      </c>
+      <c r="W73" t="n">
+        <v>52</v>
+      </c>
+      <c r="X73" t="n">
+        <v>158</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>7132</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>2.797173240178983</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0.6330900243309002</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0.487609126984127</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>0.7606349206349207</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>0.7606349206349207</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>0.7606349206349207</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>-0.02478174603174603</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>-0.02478174603174588</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>[[103, 377], [377, 1198]]</t>
+        </is>
+      </c>
+      <c r="AJ73" t="n">
+        <v>0.4594517195767196</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>0.7355736454104307</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>0.2145833333333333</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>0.7606349206349207</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>103</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>377</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>377</v>
+      </c>
+      <c r="AQ73" t="n">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>32</v>
+      </c>
+      <c r="D74" t="n">
+        <v>4.5e-06</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>0.7744760713168596</v>
+      </c>
+      <c r="G74" t="b">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.05923307531036681</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.9809076682316119</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.978641168401517</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.9918339100346021</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.9829903978052126</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.9873923527385463</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.9482442710743753</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.9480830319860948</v>
+      </c>
+      <c r="P74" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>[[2236, 59], [124, 7166]]</t>
+        </is>
+      </c>
+      <c r="R74" t="n">
+        <v>0.9977967849233887</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0.9992897602548565</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0.9742919389978214</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0.9829903978052126</v>
+      </c>
+      <c r="V74" t="n">
+        <v>2236</v>
+      </c>
+      <c r="W74" t="n">
+        <v>59</v>
+      </c>
+      <c r="X74" t="n">
+        <v>124</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>7166</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>2.91124420885332</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0.6491484184914842</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0.493015873015873</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>0.7632552404438965</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>0.7860317460317461</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>0.7744760713168596</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>-0.0144921775902559</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>-0.01446045455945932</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>[[96, 384], [337, 1238]]</t>
+        </is>
+      </c>
+      <c r="AJ74" t="n">
+        <v>0.4551997354497355</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>0.7331592080201255</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>0.7860317460317461</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>96</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>384</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>337</v>
+      </c>
+      <c r="AQ74" t="n">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>resnet50_v2</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:37:08</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>33</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1.35e-06</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>0.7749608763693271</v>
+      </c>
+      <c r="G75" t="b">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.05976822706766283</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.9797600417318727</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.9766924876946663</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.9907330567081605</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.9825788751714678</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.9866391184573002</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.9450587516453361</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.9449216250799743</v>
+      </c>
+      <c r="P75" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>[[2228, 67], [127, 7163]]</t>
+        </is>
+      </c>
+      <c r="R75" t="n">
+        <v>0.9978197967191754</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0.9993014809141219</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0.970806100217865</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0.9825788751714678</v>
+      </c>
+      <c r="V75" t="n">
+        <v>2228</v>
+      </c>
+      <c r="W75" t="n">
+        <v>67</v>
+      </c>
+      <c r="X75" t="n">
+        <v>127</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>7163</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>2.947940074150289</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.6501216545012165</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.4950992063492063</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.7641975308641975</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.7860317460317461</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0.7749608763693271</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>-0.01015208334442254</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>-0.01013177459877967</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>[[98, 382], [337, 1238]]</t>
+        </is>
+      </c>
+      <c r="AJ75" t="n">
+        <v>0.4599980158730159</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>0.7380675269033974</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>0.2041666666666667</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>0.7860317460317461</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>98</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>382</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>337</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>1238</v>
       </c>
     </row>
   </sheetData>

--- a/resultados/experimentos_entrenamiento.xlsx
+++ b/resultados/experimentos_entrenamiento.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW6"/>
+  <dimension ref="A1:CW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2634,11 +2634,358 @@
       <c r="CU6" t="n">
         <v>1</v>
       </c>
-      <c r="CV6" t="b">
+      <c r="CV6" t="n">
         <v>1</v>
       </c>
       <c r="CW6" t="n">
         <v>0.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:53:46</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>49.10522223313649</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>/Users/luisazcoitipena/Desktop/Repo TFM/TFM-UNIR/models/resnet50_v4_best.pth</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>/Users/luisazcoitipena/Desktop/Repo TFM/TFM-UNIR/resultados/experimentos_entrenamiento.xlsx</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>20</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.7819181429444105</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>{"Control": 0, "PD": 1}</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>300</v>
+      </c>
+      <c r="N7" t="n">
+        <v>65</v>
+      </c>
+      <c r="O7" t="n">
+        <v>65</v>
+      </c>
+      <c r="P7" t="n">
+        <v>14968834</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>23512130</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>data_index.csv</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>data/PPMI_Procesado_2D_Atlas</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>models</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>resultados/experimentos_entrenamiento.xlsx</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>['Control', 'PD']</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>2</v>
+      </c>
+      <c r="X7" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>adamw</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>plateau</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>layer4</t>
+        </is>
+      </c>
+      <c r="AK7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AN7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="AR7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.1046691254873449</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.9600417318727178</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.9602961349148713</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.9873006914068012</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.9598079561042524</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.9733602281421715</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.894942225310844</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.8935157085181951</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>9585</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>[[2205, 90], [293, 6997]]</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.9931630460445116</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.9978255784916257</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.9607843137254902</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.9598079561042524</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2205</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>90</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>293</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>6997</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>2.848084348367658</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.6525547445255474</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.469890873015873</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0.7533843437316068</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0.8126984126984127</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.7819181429444105</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>-0.06732360578353389</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>-0.06615948031564711</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>2055</v>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>[[61, 419], [295, 1280]]</t>
+        </is>
+      </c>
+      <c r="BU7" t="n">
+        <v>0.4365085978835979</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.7368814774309924</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0.1270833333333333</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0.8126984126984127</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>61</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>419</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>295</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>1280</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>2.210545391003871</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.6982968369829684</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.5392385392385393</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0.7764705882352941</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.8098159509202454</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.08877058630943896</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.08686304020640723</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>2055</v>
+      </c>
+      <c r="CL7" t="inlineStr">
+        <is>
+          <t>[[115, 380], [240, 1320]]</t>
+        </is>
+      </c>
+      <c r="CM7" t="n">
+        <v>0.5719289044289044</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0.8000350332739663</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0.2323232323232323</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>115</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>380</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>240</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>1320</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -2652,7 +2999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ75"/>
+  <dimension ref="A1:AQ103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13304,6 +13651,3954 @@
       </c>
       <c r="AQ75" t="n">
         <v>1238</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>0.6483050847457628</v>
+      </c>
+      <c r="G76" t="b">
+        <v>1</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.6669835724181412</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.6042775169535733</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.5910191236988622</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.8184301584410855</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.6164609053497943</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.7032313590485878</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0.1570428302892106</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.1435009525384594</v>
+      </c>
+      <c r="P76" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>[[1298, 997], [2796, 4494]]</t>
+        </is>
+      </c>
+      <c r="R76" t="n">
+        <v>0.6276233895478631</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0.8357151174824824</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0.5655773420479303</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0.6164609053497943</v>
+      </c>
+      <c r="V76" t="n">
+        <v>1298</v>
+      </c>
+      <c r="W76" t="n">
+        <v>997</v>
+      </c>
+      <c r="X76" t="n">
+        <v>2796</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>4494</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>0.7813837033118645</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0.5153284671532846</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>0.4383035714285715</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>0.7303102625298329</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>0.5828571428571429</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>0.6483050847457628</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>-0.1071227797148469</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>-0.1002951279694229</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>[[141, 339], [657, 918]]</t>
+        </is>
+      </c>
+      <c r="AJ76" t="n">
+        <v>0.4226521164021164</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>0.7227060530730315</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>0.5828571428571429</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>141</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>339</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>657</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>2</v>
+      </c>
+      <c r="D77" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>0.6232902033271719</v>
+      </c>
+      <c r="G77" t="b">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.5823610306345801</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.6864893062076161</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.6873113854595336</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.8750218799229826</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.6857338820301784</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.768899484734292</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0.3257988106606056</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.3032373313651787</v>
+      </c>
+      <c r="P77" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>[[1581, 714], [2291, 4999]]</t>
+        </is>
+      </c>
+      <c r="R77" t="n">
+        <v>0.7596029419236068</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0.9049432629503308</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0.6888888888888889</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0.6857338820301784</v>
+      </c>
+      <c r="V77" t="n">
+        <v>1581</v>
+      </c>
+      <c r="W77" t="n">
+        <v>714</v>
+      </c>
+      <c r="X77" t="n">
+        <v>2291</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>4999</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>0.8905277867676857</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>0.5041362530413626</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>0.4686607142857143</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>0.7460176991150442</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>0.5352380952380953</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>0.6232902033271719</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>-0.05330523951556161</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>-0.04740218329144308</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>[[193, 287], [732, 843]]</t>
+        </is>
+      </c>
+      <c r="AJ77" t="n">
+        <v>0.4435066137566138</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>0.7298523459478771</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>0.4020833333333333</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>0.5352380952380953</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>193</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>287</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>732</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>3</v>
+      </c>
+      <c r="D78" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>0.6925151719487526</v>
+      </c>
+      <c r="G78" t="b">
+        <v>1</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.4941899075754372</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.7486697965571205</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.7569999193092876</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.9120378186729697</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.7410150891632373</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.8176795580110497</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0.4514275453103806</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.4268879067414112</v>
+      </c>
+      <c r="P78" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>[[1774, 521], [1888, 5402]]</t>
+        </is>
+      </c>
+      <c r="R78" t="n">
+        <v>0.8383802983165527</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0.9410435841668356</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0.7729847494553377</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0.7410150891632373</v>
+      </c>
+      <c r="V78" t="n">
+        <v>1774</v>
+      </c>
+      <c r="W78" t="n">
+        <v>521</v>
+      </c>
+      <c r="X78" t="n">
+        <v>1888</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>5402</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>1.161944944841148</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>0.5562043795620438</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>0.4468650793650794</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>0.7383177570093458</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>0.652063492063492</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>0.6925151719487526</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>-0.09614425199597178</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>-0.09377407381469283</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>[[116, 364], [548, 1027]]</t>
+        </is>
+      </c>
+      <c r="AJ78" t="n">
+        <v>0.4129193121693122</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>0.7207167099612214</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>0.2416666666666667</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>0.652063492063492</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>116</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>364</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>548</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>4</v>
+      </c>
+      <c r="D79" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>0.6668979875086746</v>
+      </c>
+      <c r="G79" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.4250749164312907</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.7962441314553991</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.7990236423787622</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.9279871692060946</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.7936899862825789</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.8556007393715342</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.5352417717387431</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.5166768329876785</v>
+      </c>
+      <c r="P79" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>[[1846, 449], [1504, 5786]]</t>
+        </is>
+      </c>
+      <c r="R79" t="n">
+        <v>0.8856238139212399</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0.9580827502489999</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0.8043572984749455</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0.7936899862825789</v>
+      </c>
+      <c r="V79" t="n">
+        <v>1846</v>
+      </c>
+      <c r="W79" t="n">
+        <v>449</v>
+      </c>
+      <c r="X79" t="n">
+        <v>1504</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>5786</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>1.27950052252071</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0.5328467153284672</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>0.4446626984126984</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>0.7352716143840857</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>0.6101587301587301</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>0.6668979875086746</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>-0.09732407360618489</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>-0.0926855205875512</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>[[134, 346], [614, 961]]</t>
+        </is>
+      </c>
+      <c r="AJ79" t="n">
+        <v>0.4368214285714286</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>0.7360402142321639</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>0.2791666666666667</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>0.6101587301587301</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>134</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>346</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>614</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>5</v>
+      </c>
+      <c r="D80" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>0.7137203166226913</v>
+      </c>
+      <c r="G80" t="b">
+        <v>1</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.3711719621235216</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.8309859154929577</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.8294763172758816</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.9384472626043922</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.8323731138545953</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.8822332073277116</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0.6001831108997882</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.5867762656818084</v>
+      </c>
+      <c r="P80" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>[[1897, 398], [1222, 6068]]</t>
+        </is>
+      </c>
+      <c r="R80" t="n">
+        <v>0.9144220602430883</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0.9695774628261189</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0.8265795206971678</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0.8323731138545953</v>
+      </c>
+      <c r="V80" t="n">
+        <v>1897</v>
+      </c>
+      <c r="W80" t="n">
+        <v>398</v>
+      </c>
+      <c r="X80" t="n">
+        <v>1222</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>6068</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>1.331898348522882</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0.5776155717761557</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>0.4528670634920635</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>0.7426218256691832</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>0.686984126984127</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>0.7137203166226913</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>-0.087808189749267</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>-0.08684446231743648</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>[[105, 375], [493, 1082]]</t>
+        </is>
+      </c>
+      <c r="AJ80" t="n">
+        <v>0.4378055555555556</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>0.7298162479795007</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>0.686984126984127</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>105</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>375</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>493</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>6</v>
+      </c>
+      <c r="D81" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>0.7095064590924147</v>
+      </c>
+      <c r="G81" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.3243904571515791</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.8577986437141367</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.8574033728717825</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.9500379650721337</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.858161865569273</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.9017657657657657</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.6578172145663022</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.6467429593531548</v>
+      </c>
+      <c r="P81" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>[[1966, 329], [1034, 6256]]</t>
+        </is>
+      </c>
+      <c r="R81" t="n">
+        <v>0.9357648433554187</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0.977487445858443</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0.856644880174292</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0.858161865569273</v>
+      </c>
+      <c r="V81" t="n">
+        <v>1966</v>
+      </c>
+      <c r="W81" t="n">
+        <v>329</v>
+      </c>
+      <c r="X81" t="n">
+        <v>1034</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>6256</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>1.630024549850872</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>0.5732360097323601</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>0.4514583333333334</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>0.7416897506925207</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>0.7095064590924147</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>-0.08986723409651358</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>-0.08867102199106602</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>[[107, 373], [504, 1071]]</t>
+        </is>
+      </c>
+      <c r="AJ81" t="n">
+        <v>0.4331256613756614</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>0.7313375857525726</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>0.2229166666666667</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>107</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>373</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>504</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>7</v>
+      </c>
+      <c r="D82" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>0.7242611237414746</v>
+      </c>
+      <c r="G82" t="b">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.2979517526407695</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.8672926447574335</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.8682724118453966</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.9549440580586634</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.8663923182441701</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.9085155350978136</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0.6796273842915147</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.6690316338796212</v>
+      </c>
+      <c r="P82" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>[[1997, 298], [974, 6316]]</t>
+        </is>
+      </c>
+      <c r="R82" t="n">
+        <v>0.9456877687822577</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0.9816174202404695</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0.8701525054466231</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0.8663923182441701</v>
+      </c>
+      <c r="V82" t="n">
+        <v>1997</v>
+      </c>
+      <c r="W82" t="n">
+        <v>298</v>
+      </c>
+      <c r="X82" t="n">
+        <v>974</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>6316</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>1.705257742016275</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>0.5868613138686132</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>0.4487599206349207</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>0.7413563829787234</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>0.707936507936508</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>0.7242611237414746</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>-0.09788157966394878</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>-0.09746846192313852</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>[[91, 389], [460, 1115]]</t>
+        </is>
+      </c>
+      <c r="AJ82" t="n">
+        <v>0.4177513227513228</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>0.7216880040967752</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>0.1895833333333333</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>0.707936507936508</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>91</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>389</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>460</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>8</v>
+      </c>
+      <c r="D83" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>0.7270358306188925</v>
+      </c>
+      <c r="G83" t="b">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.248639607588077</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.8906624934793949</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.8933389816832082</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0.9652653548002386</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.8882030178326474</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.9251321617373911</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0.7324629064580923</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0.7237948877851771</v>
+      </c>
+      <c r="P83" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>[[2062, 233], [815, 6475]]</t>
+        </is>
+      </c>
+      <c r="R83" t="n">
+        <v>0.962455687350386</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0.9876040606070442</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0.8984749455337691</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0.8882030178326474</v>
+      </c>
+      <c r="V83" t="n">
+        <v>2062</v>
+      </c>
+      <c r="W83" t="n">
+        <v>233</v>
+      </c>
+      <c r="X83" t="n">
+        <v>815</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>6475</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>1.907690068173002</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>0.5922141119221411</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>0.4594940476190476</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>0.7464882943143812</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>0.7270358306188925</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>-0.07698305317899042</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>-0.07657539384846213</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[[101, 379], [459, 1116]]</t>
+        </is>
+      </c>
+      <c r="AJ83" t="n">
+        <v>0.4364854497354498</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>0.7397791397135249</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>0.2104166666666667</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>0.7085714285714285</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>101</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>379</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>459</v>
+      </c>
+      <c r="AQ83" t="n">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>9</v>
+      </c>
+      <c r="D84" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>0.6920762286860582</v>
+      </c>
+      <c r="G84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.2318415988763298</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.9003651538862807</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.9006132494149923</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.9665635586978937</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.9001371742112483</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.932168477874849</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0.7522096929538417</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.7454738604413713</v>
+      </c>
+      <c r="P84" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>[[2068, 227], [728, 6562]]</t>
+        </is>
+      </c>
+      <c r="R84" t="n">
+        <v>0.9675011879466007</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0.9891781052102058</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0.9010893246187364</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0.9001371742112483</v>
+      </c>
+      <c r="V84" t="n">
+        <v>2068</v>
+      </c>
+      <c r="W84" t="n">
+        <v>227</v>
+      </c>
+      <c r="X84" t="n">
+        <v>728</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>6562</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>1.945350923329374</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>0.5518248175182482</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>0.4316964285714285</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>0.7309322033898306</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>0.6571428571428571</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>0.6920762286860582</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>-0.1248683146689059</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>-0.122501267714644</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>[[99, 381], [540, 1035]]</t>
+        </is>
+      </c>
+      <c r="AJ84" t="n">
+        <v>0.4190939153439154</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>0.7291439721176262</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>0.20625</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>0.6571428571428571</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>99</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>381</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>540</v>
+      </c>
+      <c r="AQ84" t="n">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>10</v>
+      </c>
+      <c r="D85" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>0.6818956699624957</v>
+      </c>
+      <c r="G85" t="b">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.2131460117085812</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.9136150234741784</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.9142499798273219</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0.9716788321167883</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.9130315500685872</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.9414427157001415</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0.7829312891833154</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.7774362080714773</v>
+      </c>
+      <c r="P85" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>[[2101, 194], [634, 6656]]</t>
+        </is>
+      </c>
+      <c r="R85" t="n">
+        <v>0.9723327087274477</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0.9909346682044144</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0.9154684095860567</v>
+      </c>
+      <c r="U85" t="n">
+        <v>0.9130315500685872</v>
+      </c>
+      <c r="V85" t="n">
+        <v>2101</v>
+      </c>
+      <c r="W85" t="n">
+        <v>194</v>
+      </c>
+      <c r="X85" t="n">
+        <v>634</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>6656</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>1.813816284727296</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>0.545985401459854</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>0.4445436507936508</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>0.7363770250368189</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>0.6349206349206349</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>0.6818956699624957</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>-0.09912333265797843</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>-0.0958496583534092</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>[[122, 358], [575, 1000]]</t>
+        </is>
+      </c>
+      <c r="AJ85" t="n">
+        <v>0.4297387566137566</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>0.7288434867289292</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>0.2541666666666667</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>0.6349206349206349</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>122</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>358</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>575</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>11</v>
+      </c>
+      <c r="D86" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>0.7355584082156611</v>
+      </c>
+      <c r="G86" t="b">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.1950511277106726</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.9183098591549296</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.9185306221253933</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.9729611862189271</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.9181069958847736</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.9447385136565742</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0.7935710076313962</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.7886736078641563</v>
+      </c>
+      <c r="P86" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>[[2109, 186], [597, 6693]]</t>
+        </is>
+      </c>
+      <c r="R86" t="n">
+        <v>0.9770406232909259</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0.9925137033667174</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0.918954248366013</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0.9181069958847736</v>
+      </c>
+      <c r="V86" t="n">
+        <v>2109</v>
+      </c>
+      <c r="W86" t="n">
+        <v>186</v>
+      </c>
+      <c r="X86" t="n">
+        <v>597</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>6693</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>2.178549090151079</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>0.5990267639902677</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>0.4523511904761905</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>0.7436729396495781</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>0.7276190476190476</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>0.7355584082156611</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>-0.09310222693186695</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>-0.09300749404542907</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>[[85, 395], [429, 1146]]</t>
+        </is>
+      </c>
+      <c r="AJ86" t="n">
+        <v>0.4182863756613757</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>0.7288493015690738</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>0.1770833333333333</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>0.7276190476190476</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>395</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>429</v>
+      </c>
+      <c r="AQ86" t="n">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>12</v>
+      </c>
+      <c r="D87" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>0.7029009669889963</v>
+      </c>
+      <c r="G87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.1762225886240376</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.9300991131977048</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.9295650770596304</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.9763960852043754</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.9305898491083676</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.9529428290490237</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0.8209734296916359</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0.8173994487820233</v>
+      </c>
+      <c r="P87" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>[[2131, 164], [506, 6784]]</t>
+        </is>
+      </c>
+      <c r="R87" t="n">
+        <v>0.9809498791133585</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0.9937937227967556</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0.9285403050108932</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0.9305898491083676</v>
+      </c>
+      <c r="V87" t="n">
+        <v>2131</v>
+      </c>
+      <c r="W87" t="n">
+        <v>164</v>
+      </c>
+      <c r="X87" t="n">
+        <v>506</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>6784</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>2.010111190860869</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>0.5664233576642336</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>0.4491865079365079</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>0.7401685393258427</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>0.6692063492063492</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>0.7029009669889963</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>-0.09321810309128302</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>-0.09160906074778885</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>[[110, 370], [521, 1054]]</t>
+        </is>
+      </c>
+      <c r="AJ87" t="n">
+        <v>0.42807208994709</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>0.736257451747703</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>0.2291666666666667</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>0.6692063492063492</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>370</v>
+      </c>
+      <c r="AP87" t="n">
+        <v>521</v>
+      </c>
+      <c r="AQ87" t="n">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>13</v>
+      </c>
+      <c r="D88" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>0.7464477423429112</v>
+      </c>
+      <c r="G88" t="b">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.1573841607782078</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.9371935315597287</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.9381102235132737</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.9801838024124067</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.9363511659807956</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.9577662410551424</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0.838891126938579</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0.835558359815637</v>
+      </c>
+      <c r="P88" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>[[2157, 138], [464, 6826]]</t>
+        </is>
+      </c>
+      <c r="R88" t="n">
+        <v>0.9849154988927441</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0.9950091617422605</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0.9398692810457516</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0.9363511659807956</v>
+      </c>
+      <c r="V88" t="n">
+        <v>2157</v>
+      </c>
+      <c r="W88" t="n">
+        <v>138</v>
+      </c>
+      <c r="X88" t="n">
+        <v>464</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>6826</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>2.40014597273221</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>0.6092457420924574</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>0.4481547619047619</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>0.742462311557789</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>0.7504761904761905</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>0.7464477423429112</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>-0.1050117121621974</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>-0.1049829749193947</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>[[70, 410], [393, 1182]]</t>
+        </is>
+      </c>
+      <c r="AJ88" t="n">
+        <v>0.4283472222222223</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>0.7399948662836526</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>0.1458333333333333</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>0.7504761904761905</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>410</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>393</v>
+      </c>
+      <c r="AQ88" t="n">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>14</v>
+      </c>
+      <c r="D89" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>0.7288573273079406</v>
+      </c>
+      <c r="G89" t="b">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.140160233634303</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.9426186750130412</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.9419753086419753</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0.9806046776953794</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.9432098765432099</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.9615438400223745</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0.8512208753198409</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0.8487290138138883</v>
+      </c>
+      <c r="P89" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>[[2159, 136], [414, 6876]]</t>
+        </is>
+      </c>
+      <c r="R89" t="n">
+        <v>0.9881262719994264</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0.9961700990010174</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0.9407407407407408</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0.9432098765432099</v>
+      </c>
+      <c r="V89" t="n">
+        <v>2159</v>
+      </c>
+      <c r="W89" t="n">
+        <v>136</v>
+      </c>
+      <c r="X89" t="n">
+        <v>414</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>6876</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>2.536379545680508</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>0.5912408759124088</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>0.4479960317460318</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>0.7413000656598818</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>0.7168253968253968</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>0.7288573273079406</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>-0.1004665780294039</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>-0.100233278519255</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>[[86, 394], [446, 1129]]</t>
+        </is>
+      </c>
+      <c r="AJ89" t="n">
+        <v>0.4118611111111111</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>0.7308304713635989</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>0.1791666666666667</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>0.7168253968253968</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>86</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>394</v>
+      </c>
+      <c r="AP89" t="n">
+        <v>446</v>
+      </c>
+      <c r="AQ89" t="n">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>15</v>
+      </c>
+      <c r="D90" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>0.6714677640603567</v>
+      </c>
+      <c r="G90" t="b">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.1495579196626965</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.9437663015127804</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.9425804889857177</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0.9804982206405694</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.9448559670781893</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.9623471882640586</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0.8537568910757802</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0.8514776939048765</v>
+      </c>
+      <c r="P90" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>[[2158, 137], [402, 6888]]</t>
+        </is>
+      </c>
+      <c r="R90" t="n">
+        <v>0.9859437376535739</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0.9951533120875031</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0.9403050108932461</v>
+      </c>
+      <c r="U90" t="n">
+        <v>0.9448559670781893</v>
+      </c>
+      <c r="V90" t="n">
+        <v>2158</v>
+      </c>
+      <c r="W90" t="n">
+        <v>137</v>
+      </c>
+      <c r="X90" t="n">
+        <v>402</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>6888</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>2.153448349193935</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>0.5338199513381995</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>0.4337103174603175</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>0.7300521998508576</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>0.6215873015873016</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>0.6714677640603567</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>-0.1178076079336517</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>-0.1133676048930288</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>[[118, 362], [596, 979]]</t>
+        </is>
+      </c>
+      <c r="AJ90" t="n">
+        <v>0.4189973544973545</v>
+      </c>
+      <c r="AK90" t="n">
+        <v>0.732458651813799</v>
+      </c>
+      <c r="AL90" t="n">
+        <v>0.2458333333333333</v>
+      </c>
+      <c r="AM90" t="n">
+        <v>0.6215873015873016</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>118</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>362</v>
+      </c>
+      <c r="AP90" t="n">
+        <v>596</v>
+      </c>
+      <c r="AQ90" t="n">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>16</v>
+      </c>
+      <c r="D91" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>0.7510204081632653</v>
+      </c>
+      <c r="G91" t="b">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.1296287581239073</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.9497130933750652</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.9485798434600177</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0.982563084774596</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.9507544581618655</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.9663970998326826</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0.8684824755262275</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.8666287335536571</v>
+      </c>
+      <c r="P91" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>[[2172, 123], [359, 6931]]</t>
+        </is>
+      </c>
+      <c r="R91" t="n">
+        <v>0.9897158491502073</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0.9966693276538431</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0.9464052287581699</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0.9507544581618655</v>
+      </c>
+      <c r="V91" t="n">
+        <v>2172</v>
+      </c>
+      <c r="W91" t="n">
+        <v>123</v>
+      </c>
+      <c r="X91" t="n">
+        <v>359</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>6931</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>2.662155884373797</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>0.6141119221411192</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>0.4484325396825397</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>0.7593650793650794</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>0.7510204081632653</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>-0.1059433479175248</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>-0.1058170899282407</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>[[66, 414], [379, 1196]]</t>
+        </is>
+      </c>
+      <c r="AJ91" t="n">
+        <v>0.4206626984126984</v>
+      </c>
+      <c r="AK91" t="n">
+        <v>0.7402101530431884</v>
+      </c>
+      <c r="AL91" t="n">
+        <v>0.1375</v>
+      </c>
+      <c r="AM91" t="n">
+        <v>0.7593650793650794</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>66</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>414</v>
+      </c>
+      <c r="AP91" t="n">
+        <v>379</v>
+      </c>
+      <c r="AQ91" t="n">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>17</v>
+      </c>
+      <c r="D92" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>0.7462025316455696</v>
+      </c>
+      <c r="G92" t="b">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.1281132510729643</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.9501304121022431</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.9491527475187607</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.9828466118514319</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.9510288065843622</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.9666759620747351</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0.8695916585232569</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0.8677355490428384</v>
+      </c>
+      <c r="P92" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>[[2174, 121], [357, 6933]]</t>
+        </is>
+      </c>
+      <c r="R92" t="n">
+        <v>0.9896518046328423</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0.9965173935889351</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0.947276688453159</v>
+      </c>
+      <c r="U92" t="n">
+        <v>0.9510288065843622</v>
+      </c>
+      <c r="V92" t="n">
+        <v>2174</v>
+      </c>
+      <c r="W92" t="n">
+        <v>121</v>
+      </c>
+      <c r="X92" t="n">
+        <v>357</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>6933</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>2.492752975500993</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>0.6097323600973236</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>0.4513690476190476</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>0.7438485804416404</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>0.7485714285714286</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>0.7462025316455696</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>-0.09798060256644844</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>-0.09797142000599579</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>[[74, 406], [396, 1179]]</t>
+        </is>
+      </c>
+      <c r="AJ92" t="n">
+        <v>0.4211818783068784</v>
+      </c>
+      <c r="AK92" t="n">
+        <v>0.7443631872322072</v>
+      </c>
+      <c r="AL92" t="n">
+        <v>0.1541666666666667</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>0.7485714285714286</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>74</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>406</v>
+      </c>
+      <c r="AP92" t="n">
+        <v>396</v>
+      </c>
+      <c r="AQ92" t="n">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>18</v>
+      </c>
+      <c r="D93" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>0.7725030826140568</v>
+      </c>
+      <c r="G93" t="b">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.1048569103859338</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.9605633802816902</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.9601912369886226</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.9868977176669484</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.9609053497942387</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.9737281067556297</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0.8960197019153145</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0.8947380806702123</v>
+      </c>
+      <c r="P93" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>[[2202, 93], [285, 7005]]</t>
+        </is>
+      </c>
+      <c r="R93" t="n">
+        <v>0.9932311250975012</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0.9977772124425429</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0.9594771241830066</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0.9609053497942387</v>
+      </c>
+      <c r="V93" t="n">
+        <v>2202</v>
+      </c>
+      <c r="W93" t="n">
+        <v>93</v>
+      </c>
+      <c r="X93" t="n">
+        <v>285</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>7005</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>2.983440462980247</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>0.6408759124087591</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>0.4644444444444444</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>0.7507489514679448</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>0.7955555555555556</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>0.7725030826140568</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>-0.07703295212887763</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>-0.07630564840639575</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>[[64, 416], [322, 1253]]</t>
+        </is>
+      </c>
+      <c r="AJ93" t="n">
+        <v>0.4138730158730158</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>0.7288776854297443</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>0.7955555555555556</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>64</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>416</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>322</v>
+      </c>
+      <c r="AQ93" t="n">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>19</v>
+      </c>
+      <c r="D94" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>0.773838630806846</v>
+      </c>
+      <c r="G94" t="b">
+        <v>1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.1149515318233922</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.9544079290558164</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.9534575970305817</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.9843109540636042</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.955281207133059</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.9695788374521406</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0.8802817622395146</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.8787131325371851</v>
+      </c>
+      <c r="P94" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>[[2184, 111], [326, 6964]]</t>
+        </is>
+      </c>
+      <c r="R94" t="n">
+        <v>0.9917518551392511</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0.9972715273942987</v>
+      </c>
+      <c r="T94" t="n">
+        <v>0.9516339869281045</v>
+      </c>
+      <c r="U94" t="n">
+        <v>0.955281207133059</v>
+      </c>
+      <c r="V94" t="n">
+        <v>2184</v>
+      </c>
+      <c r="W94" t="n">
+        <v>111</v>
+      </c>
+      <c r="X94" t="n">
+        <v>326</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>6964</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>2.76323731531482</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>0.6399026763990268</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>0.4529464285714286</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>0.7460223924572775</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>0.8038095238095239</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>0.773838630806846</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>-0.1049786664201807</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>-0.1032276318366814</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>[[49, 431], [309, 1266]]</t>
+        </is>
+      </c>
+      <c r="AJ94" t="n">
+        <v>0.4347367724867724</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>0.756686933080595</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>0.1020833333333333</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>0.8038095238095239</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>49</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>431</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>309</v>
+      </c>
+      <c r="AQ94" t="n">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>20</v>
+      </c>
+      <c r="D95" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>0.7819181429444105</v>
+      </c>
+      <c r="G95" t="b">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.1046691254873449</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.9600417318727178</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.9602961349148713</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0.9873006914068012</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.9598079561042524</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.9733602281421715</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0.894942225310844</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0.8935157085181951</v>
+      </c>
+      <c r="P95" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>[[2205, 90], [293, 6997]]</t>
+        </is>
+      </c>
+      <c r="R95" t="n">
+        <v>0.9931630460445116</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0.9978255784916257</v>
+      </c>
+      <c r="T95" t="n">
+        <v>0.9607843137254902</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0.9598079561042524</v>
+      </c>
+      <c r="V95" t="n">
+        <v>2205</v>
+      </c>
+      <c r="W95" t="n">
+        <v>90</v>
+      </c>
+      <c r="X95" t="n">
+        <v>293</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>6997</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>2.848084348367658</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>0.6525547445255474</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>0.469890873015873</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>0.7533843437316068</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>0.8126984126984127</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>0.7819181429444105</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>-0.06732360578353389</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>-0.06615948031564711</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>[[61, 419], [295, 1280]]</t>
+        </is>
+      </c>
+      <c r="AJ95" t="n">
+        <v>0.4365085978835979</v>
+      </c>
+      <c r="AK95" t="n">
+        <v>0.7368814774309924</v>
+      </c>
+      <c r="AL95" t="n">
+        <v>0.1270833333333333</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>0.8126984126984127</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>61</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>419</v>
+      </c>
+      <c r="AP95" t="n">
+        <v>295</v>
+      </c>
+      <c r="AQ95" t="n">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>21</v>
+      </c>
+      <c r="D96" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>0.7268593699253004</v>
+      </c>
+      <c r="G96" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.08842004945285008</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.9695357329160146</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.9692245622528847</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0.9899187902548305</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.9698216735253772</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.9797671840354767</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0.9189548753347153</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.9181640193261124</v>
+      </c>
+      <c r="P96" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>[[2223, 72], [220, 7070]]</t>
+        </is>
+      </c>
+      <c r="R96" t="n">
+        <v>0.9950056035217013</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0.9983341766635065</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0.9686274509803922</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0.9698216735253772</v>
+      </c>
+      <c r="V96" t="n">
+        <v>2223</v>
+      </c>
+      <c r="W96" t="n">
+        <v>72</v>
+      </c>
+      <c r="X96" t="n">
+        <v>220</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>7070</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>2.830795383917444</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>0.5907542579075425</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>0.4541964285714286</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>0.7440159574468085</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>0.7104761904761905</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>0.7268593699253004</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>-0.0874964672426818</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>-0.08712718077427506</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>[[95, 385], [456, 1119]]</t>
+        </is>
+      </c>
+      <c r="AJ96" t="n">
+        <v>0.4279100529100529</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>0.7429521812543172</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>0.1979166666666667</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>0.7104761904761905</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>385</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>456</v>
+      </c>
+      <c r="AQ96" t="n">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>22</v>
+      </c>
+      <c r="D97" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>0.7510307643514114</v>
+      </c>
+      <c r="G97" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.0949607235204135</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.96452790818988</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.9642903251835714</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.9883361439010681</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.9647462277091907</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.9763987227544079</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0.9061419238600115</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.9050720021392225</v>
+      </c>
+      <c r="P97" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>[[2212, 83], [257, 7033]]</t>
+        </is>
+      </c>
+      <c r="R97" t="n">
+        <v>0.9943652778898483</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0.9981518959221709</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0.9638344226579521</v>
+      </c>
+      <c r="U97" t="n">
+        <v>0.9647462277091907</v>
+      </c>
+      <c r="V97" t="n">
+        <v>2212</v>
+      </c>
+      <c r="W97" t="n">
+        <v>83</v>
+      </c>
+      <c r="X97" t="n">
+        <v>257</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>7033</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>2.96991849862166</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>0.6180048661800487</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>0.4654563492063492</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>0.7503168567807351</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>0.7517460317460317</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>0.7510307643514114</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>-0.06923830685181474</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>-0.06923772879569712</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>[[86, 394], [391, 1184]]</t>
+        </is>
+      </c>
+      <c r="AJ97" t="n">
+        <v>0.4216322751322751</v>
+      </c>
+      <c r="AK97" t="n">
+        <v>0.726719223586239</v>
+      </c>
+      <c r="AL97" t="n">
+        <v>0.1791666666666667</v>
+      </c>
+      <c r="AM97" t="n">
+        <v>0.7517460317460317</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>86</v>
+      </c>
+      <c r="AO97" t="n">
+        <v>394</v>
+      </c>
+      <c r="AP97" t="n">
+        <v>391</v>
+      </c>
+      <c r="AQ97" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>23</v>
+      </c>
+      <c r="D98" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>0.747308423052565</v>
+      </c>
+      <c r="G98" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.08434208759422966</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.9685967657798644</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.9680101670297749</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0.989357232880549</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.9691358024691358</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.9791421245928903</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0.9164531645758054</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.915653996282161</v>
+      </c>
+      <c r="P98" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>[[2219, 76], [225, 7065]]</t>
+        </is>
+      </c>
+      <c r="R98" t="n">
+        <v>0.9954929156542972</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0.9985312014784259</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0.966884531590414</v>
+      </c>
+      <c r="U98" t="n">
+        <v>0.9691358024691358</v>
+      </c>
+      <c r="V98" t="n">
+        <v>2219</v>
+      </c>
+      <c r="W98" t="n">
+        <v>76</v>
+      </c>
+      <c r="X98" t="n">
+        <v>225</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>7065</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>2.854844876913549</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>0.6116788321167883</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>0.4548115079365079</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>0.7454200884396716</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>0.7492063492063492</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>0.747308423052565</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>-0.09090908484368387</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>-0.09090364812006069</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>[[77, 403], [395, 1180]]</t>
+        </is>
+      </c>
+      <c r="AJ98" t="n">
+        <v>0.4326746031746032</v>
+      </c>
+      <c r="AK98" t="n">
+        <v>0.7400841460309429</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>0.1604166666666667</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>0.7492063492063492</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>77</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>403</v>
+      </c>
+      <c r="AP98" t="n">
+        <v>395</v>
+      </c>
+      <c r="AQ98" t="n">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>24</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1.5e-05</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>0.7593114241001565</v>
+      </c>
+      <c r="G99" t="b">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.08463989851698007</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.9678664580073031</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.9667836681997902</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0.9886618141097424</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.9688614540466393</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.9786614936954413</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0.914420901992033</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.9136546343312459</v>
+      </c>
+      <c r="P99" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>[[2214, 81], [227, 7063]]</t>
+        </is>
+      </c>
+      <c r="R99" t="n">
+        <v>0.9955571095989073</v>
+      </c>
+      <c r="S99" t="n">
+        <v>0.9985680606321919</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0.9647058823529412</v>
+      </c>
+      <c r="U99" t="n">
+        <v>0.9688614540466393</v>
+      </c>
+      <c r="V99" t="n">
+        <v>2214</v>
+      </c>
+      <c r="W99" t="n">
+        <v>81</v>
+      </c>
+      <c r="X99" t="n">
+        <v>227</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>7063</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>3.066881872209609</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>0.6257907542579075</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>0.4611210317460318</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>0.7487654320987654</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>0.7701587301587302</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>0.7593114241001565</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>-0.08053849114735206</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>-0.08037737783930687</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>[[73, 407], [362, 1213]]</t>
+        </is>
+      </c>
+      <c r="AJ99" t="n">
+        <v>0.4277414021164021</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>0.7420072212462632</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>0.1520833333333333</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>0.7701587301587302</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>73</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>407</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>362</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>25</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1.5e-05</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>0.7577367927477336</v>
+      </c>
+      <c r="G100" t="b">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.06414638089446519</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.9790297339593115</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.9778544339546518</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0.9922233023191224</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.9801097393689986</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.9861293216479194</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0.9434767316141309</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.9431780627744841</v>
+      </c>
+      <c r="P100" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>[[2239, 56], [145, 7145]]</t>
+        </is>
+      </c>
+      <c r="R100" t="n">
+        <v>0.9973989498253194</v>
+      </c>
+      <c r="S100" t="n">
+        <v>0.9991416028349047</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0.9755991285403051</v>
+      </c>
+      <c r="U100" t="n">
+        <v>0.9801097393689986</v>
+      </c>
+      <c r="V100" t="n">
+        <v>2239</v>
+      </c>
+      <c r="W100" t="n">
+        <v>56</v>
+      </c>
+      <c r="X100" t="n">
+        <v>145</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>7145</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>3.201292110823657</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>0.6228710462287105</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>0.4555952380952381</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>0.7463054187192119</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>0.7695238095238095</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>0.7577367927477336</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>-0.09229725642455364</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>-0.09207697766989287</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>[[68, 412], [363, 1212]]</t>
+        </is>
+      </c>
+      <c r="AJ100" t="n">
+        <v>0.4110886243386244</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>0.733580177570053</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>0.1416666666666667</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>0.7695238095238095</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>68</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>412</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>363</v>
+      </c>
+      <c r="AQ100" t="n">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>26</v>
+      </c>
+      <c r="D101" t="n">
+        <v>1.5e-05</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>0.7472458293988039</v>
+      </c>
+      <c r="G101" t="b">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.05454964137708513</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.980490349504434</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0.9795610425240056</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0.9929215822345593</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.9813443072702333</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.9870989996550534</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0.9473785103925056</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.9471046393498137</v>
+      </c>
+      <c r="P101" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>[[2244, 51], [136, 7154]]</t>
+        </is>
+      </c>
+      <c r="R101" t="n">
+        <v>0.9982381930062072</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0.9994539090890602</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0.9777777777777777</v>
+      </c>
+      <c r="U101" t="n">
+        <v>0.9813443072702333</v>
+      </c>
+      <c r="V101" t="n">
+        <v>2244</v>
+      </c>
+      <c r="W101" t="n">
+        <v>51</v>
+      </c>
+      <c r="X101" t="n">
+        <v>136</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>7154</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>3.355111125611911</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>0.6092457420924574</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>0.4445337301587302</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>0.7409488139825219</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>0.7536507936507937</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>0.7472458293988039</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>-0.113224261495993</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>-0.1131449270962976</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>[[65, 415], [388, 1187]]</t>
+        </is>
+      </c>
+      <c r="AJ101" t="n">
+        <v>0.3991593915343915</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>0.722205152130407</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>0.1354166666666667</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>0.7536507936507937</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>415</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>388</v>
+      </c>
+      <c r="AQ101" t="n">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>27</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1.5e-05</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>0.7620829435609604</v>
+      </c>
+      <c r="G102" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.05669132149294913</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.9798643714136672</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0.9798959089808763</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0.9936013353734873</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0.9798353909465021</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.986670350162304</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0.9459202084946554</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0.9455359165649829</v>
+      </c>
+      <c r="P102" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>[[2249, 46], [147, 7143]]</t>
+        </is>
+      </c>
+      <c r="R102" t="n">
+        <v>0.9980123785530064</v>
+      </c>
+      <c r="S102" t="n">
+        <v>0.9993693542416082</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0.9799564270152505</v>
+      </c>
+      <c r="U102" t="n">
+        <v>0.9798353909465021</v>
+      </c>
+      <c r="V102" t="n">
+        <v>2249</v>
+      </c>
+      <c r="W102" t="n">
+        <v>46</v>
+      </c>
+      <c r="X102" t="n">
+        <v>147</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>7143</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>3.301499125441206</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>0.6287104622871046</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>0.4608531746031746</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>0.7487745098039216</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>0.7758730158730158</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>0.7620829435609604</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>-0.08193268387799232</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>-0.08166475232566572</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[[70, 410], [353, 1222]]</t>
+        </is>
+      </c>
+      <c r="AJ102" t="n">
+        <v>0.4156587301587302</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>0.737877354983045</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>0.1458333333333333</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>0.7758730158730158</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>410</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>353</v>
+      </c>
+      <c r="AQ102" t="n">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>resnet50_v4</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-06-20 13:04:39</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>28</v>
+      </c>
+      <c r="D103" t="n">
+        <v>4.5e-06</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>val_f1</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>0.748898678414097</v>
+      </c>
+      <c r="G103" t="b">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.05400844431818931</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.9820552947313511</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0.9822319051077221</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0.9944429008057794</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0.9818930041152263</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.9881281060187742</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0.9517193834851193</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0.9513977330616403</v>
+      </c>
+      <c r="P103" t="n">
+        <v>9585</v>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>[[2255, 40], [132, 7158]]</t>
+        </is>
+      </c>
+      <c r="R103" t="n">
+        <v>0.9981966522319947</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0.9994122754129047</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0.9825708061002179</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0.9818930041152263</v>
+      </c>
+      <c r="V103" t="n">
+        <v>2255</v>
+      </c>
+      <c r="W103" t="n">
+        <v>40</v>
+      </c>
+      <c r="X103" t="n">
+        <v>132</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>7158</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>3.194279748911985</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>0.6116788321167883</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>0.4475694444444445</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>0.74235807860262</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>0.748898678414097</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>-0.1071123072610541</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>-0.1070314715055289</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>[[67, 413], [385, 1190]]</t>
+        </is>
+      </c>
+      <c r="AJ103" t="n">
+        <v>0.4210588624338625</v>
+      </c>
+      <c r="AK103" t="n">
+        <v>0.7325849420739675</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>0.1395833333333333</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>67</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>413</v>
+      </c>
+      <c r="AP103" t="n">
+        <v>385</v>
+      </c>
+      <c r="AQ103" t="n">
+        <v>1190</v>
       </c>
     </row>
   </sheetData>
